--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2018_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2018_tarapaca.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:52</t>
+    <t xml:space="preserve">2026-09-24 00:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,10 +672,10 @@
         <v>0.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="9">
@@ -695,10 +695,10 @@
         <v>0.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="10">
@@ -718,10 +718,10 @@
         <v>0.04</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="11">
@@ -732,19 +732,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="12">
